--- a/reports/Debug-purgatory-20260111/For The Day (Actual)_Budget.xlsx
+++ b/reports/Debug-purgatory-20260111/For The Day (Actual)_Budget.xlsx
@@ -43,6 +43,72 @@
     <t>D6215</t>
   </si>
   <si>
+    <t>99150</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8030</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D4056</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>D5810</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D4053</t>
+  </si>
+  <si>
+    <t>D4055</t>
+  </si>
+  <si>
+    <t>D5205</t>
+  </si>
+  <si>
+    <t>D5207</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -67,72 +133,6 @@
     <t>D6800</t>
   </si>
   <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D4053</t>
-  </si>
-  <si>
-    <t>D4055</t>
-  </si>
-  <si>
-    <t>D5205</t>
-  </si>
-  <si>
-    <t>D5207</t>
-  </si>
-  <si>
-    <t>D6710</t>
-  </si>
-  <si>
-    <t>D6750</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D4056</t>
-  </si>
-  <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>D5810</t>
-  </si>
-  <si>
-    <t>99150</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8030</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
     <t>99100</t>
   </si>
   <si>
@@ -199,6 +199,72 @@
     <t>Housekeeping</t>
   </si>
   <si>
+    <t>Comp Tickets</t>
+  </si>
+  <si>
+    <t>Vehicle Maintenance</t>
+  </si>
+  <si>
+    <t>F&amp;B Admin</t>
+  </si>
+  <si>
+    <t>Powderhouse</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>Branded</t>
+  </si>
+  <si>
+    <t>Purgy's</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>Expert Edge</t>
+  </si>
+  <si>
+    <t>Purg Sports Main Ave</t>
+  </si>
+  <si>
+    <t>Waffle Cabin</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
     <t>Mountain G&amp;A</t>
   </si>
   <si>
@@ -221,72 +287,6 @@
   </si>
   <si>
     <t>Commercial Tenants</t>
-  </si>
-  <si>
-    <t>Lift Operations</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
-  </si>
-  <si>
-    <t>Tickets</t>
-  </si>
-  <si>
-    <t>Expert Edge</t>
-  </si>
-  <si>
-    <t>Purg Sports Main Ave</t>
-  </si>
-  <si>
-    <t>Waffle Cabin</t>
-  </si>
-  <si>
-    <t>Paradise</t>
-  </si>
-  <si>
-    <t>Accounting/Mgmt Services</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>IT Services</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>Branded</t>
-  </si>
-  <si>
-    <t>Purgy's</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Comp Tickets</t>
-  </si>
-  <si>
-    <t>Vehicle Maintenance</t>
-  </si>
-  <si>
-    <t>F&amp;B Admin</t>
-  </si>
-  <si>
-    <t>Powderhouse</t>
-  </si>
-  <si>
-    <t>General Administration</t>
-  </si>
-  <si>
-    <t>Executive</t>
-  </si>
-  <si>
-    <t>HR</t>
   </si>
   <si>
     <t>Daily Winter Ticketed</t>
@@ -802,7 +802,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="2">
-        <v>85280.56</v>
+        <v>22626.14</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>59</v>
@@ -855,10 +855,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2">
-        <v>297.99</v>
+        <v>151.00</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>61</v>
@@ -872,7 +872,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="2">
-        <v>381.50</v>
+        <v>437.23</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>62</v>
@@ -880,604 +880,604 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>11930.88</v>
+        <v>1066.11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C16" s="2">
-        <v>553.90</v>
+        <v>970.50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="2">
-        <v>1090.15</v>
+        <v>4537.84</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="2">
-        <v>313.93</v>
+        <v>321.12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>720.12</v>
+        <v>1180.41</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="2">
-        <v>391.37</v>
+        <v>823.71</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>1030.10</v>
+        <v>0.00</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2">
-        <v>180.00</v>
+        <v>3365.12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>221.25</v>
+        <v>138.75</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2">
-        <v>1139.00</v>
+        <v>2925.10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="2">
-        <v>863.28</v>
+        <v>12594.14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="2">
-        <v>0.00</v>
+        <v>201.25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="2">
-        <v>5553.77</v>
+        <v>0.00</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="2">
-        <v>808.20</v>
+        <v>5553.77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>4950.80</v>
+        <v>808.20</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C30" s="2">
-        <v>1204.15</v>
+        <v>4950.80</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" s="2">
-        <v>140480.50</v>
+        <v>1204.15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" s="2">
-        <v>586.26</v>
+        <v>132675.30</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="2">
-        <v>2509.49</v>
+        <v>586.26</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="2">
-        <v>2776.03</v>
+        <v>2509.49</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2">
-        <v>649.76</v>
+        <v>2010.49</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C36" s="2">
-        <v>183.83</v>
+        <v>649.76</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2">
-        <v>1012.32</v>
+        <v>183.83</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2">
-        <v>1295.78</v>
+        <v>938.34</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="2">
-        <v>4419.48</v>
+        <v>1295.78</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C40" s="2">
-        <v>1190.63</v>
+        <v>3986.78</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" s="2">
-        <v>1745.45</v>
+        <v>1190.63</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C42" s="2">
-        <v>936.69</v>
+        <v>1745.45</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2">
-        <v>1635.79</v>
+        <v>936.69</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44" s="2">
-        <v>693.06</v>
+        <v>1635.79</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="2">
-        <v>0.00</v>
+        <v>693.06</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2">
-        <v>4282.88</v>
+        <v>297.99</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="2">
-        <v>138.75</v>
+        <v>381.50</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C48" s="2">
-        <v>2925.10</v>
+        <v>9407.04</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>13192.04</v>
+        <v>553.90</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C50" s="2">
-        <v>201.25</v>
+        <v>1090.15</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="2">
-        <v>0.00</v>
+        <v>313.93</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C52" s="2">
-        <v>151.00</v>
+        <v>720.12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C53" s="2">
-        <v>437.23</v>
+        <v>391.37</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C54" s="2">
-        <v>1066.11</v>
+        <v>1030.10</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C55" s="2">
-        <v>970.50</v>
+        <v>180.00</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C56" s="2">
-        <v>4738.94</v>
+        <v>221.25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C57" s="2">
-        <v>321.12</v>
+        <v>1139.00</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1485,10 +1485,10 @@
         <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C58" s="2">
-        <v>1180.41</v>
+        <v>863.28</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>89</v>
@@ -1499,10 +1499,10 @@
         <v>38</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C59" s="2">
-        <v>823.71</v>
+        <v>0.00</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>90</v>
@@ -1614,7 +1614,7 @@
         <v>50</v>
       </c>
       <c r="C67" s="2">
-        <v>6891.44</v>
+        <v>6471.78</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>95</v>
@@ -1642,7 +1642,7 @@
         <v>50</v>
       </c>
       <c r="C69" s="2">
-        <v>2248.09</v>
+        <v>1931.25</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>96</v>
